--- a/data/trans_dic/P1428-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P1428-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,28%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,54; 8,95</t>
+          <t>3,63; 9,13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,25; 7,41</t>
+          <t>2,28; 7,71</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,22; 8,56</t>
+          <t>3,24; 9,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,58; 5,28</t>
+          <t>1,4; 4,82</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,42; 18,13</t>
+          <t>9,41; 17,81</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,88; 12,03</t>
+          <t>5,07; 12,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,5; 12,65</t>
+          <t>5,74; 13,19</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,02; 10,78</t>
+          <t>5,66; 9,92</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,13; 12,39</t>
+          <t>7,05; 12,15</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4,19; 8,44</t>
+          <t>4,15; 8,54</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,19; 9,6</t>
+          <t>5,23; 9,96</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,11; 6,88</t>
+          <t>3,95; 6,65</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,45%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,99; 6,63</t>
+          <t>3,07; 7,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,59; 5,2</t>
+          <t>1,62; 5,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,7; 4,78</t>
+          <t>1,76; 4,93</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,42; 6,12</t>
+          <t>2,44; 5,76</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>15,25; 21,9</t>
+          <t>14,87; 22,06</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,13; 12,34</t>
+          <t>7,13; 12,06</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,11; 12,28</t>
+          <t>6,95; 11,92</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,45; 11,46</t>
+          <t>7,16; 11,1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,46; 13,51</t>
+          <t>9,74; 13,83</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,87; 7,96</t>
+          <t>4,76; 7,89</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,79; 8,08</t>
+          <t>4,78; 8,04</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,25; 7,91</t>
+          <t>5,15; 7,88</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,24%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,11; 6,69</t>
+          <t>2,09; 6,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,49; 10,52</t>
+          <t>4,63; 10,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,3; 6,34</t>
+          <t>2,04; 6,27</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,1; 8,86</t>
+          <t>4,11; 8,63</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14,01; 22,44</t>
+          <t>14,28; 22,89</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,93; 18,91</t>
+          <t>11,25; 19,07</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,11; 10,87</t>
+          <t>5,01; 11,07</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12,93; 19,47</t>
+          <t>12,85; 18,86</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8,84; 13,82</t>
+          <t>9,06; 14,2</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9,0; 13,88</t>
+          <t>8,75; 13,7</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,23; 7,92</t>
+          <t>4,11; 7,74</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9,27; 13,31</t>
+          <t>9,63; 13,32</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>15,88%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,29; 9,42</t>
+          <t>4,39; 9,74</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,63; 7,02</t>
+          <t>2,62; 7,2</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,41; 6,68</t>
+          <t>2,41; 6,79</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,35; 12,98</t>
+          <t>6,06; 11,76</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>13,75; 21,67</t>
+          <t>13,66; 20,88</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,53; 15,01</t>
+          <t>8,42; 14,92</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,74; 17,06</t>
+          <t>9,66; 17,21</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,38; 23,81</t>
+          <t>19,25; 26,22</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,86; 14,78</t>
+          <t>9,76; 14,55</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6,14; 10,22</t>
+          <t>6,53; 10,35</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6,74; 10,93</t>
+          <t>6,65; 10,85</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10,42; 17,62</t>
+          <t>13,74; 18,23</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>11,87%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,63; 12,62</t>
+          <t>4,44; 12,1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,64; 9,27</t>
+          <t>2,55; 9,08</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,18; 6,31</t>
+          <t>1,28; 6,21</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,33; 8,3</t>
+          <t>3,41; 8,13</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,92; 26,45</t>
+          <t>15,0; 26,78</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,92; 20,87</t>
+          <t>11,38; 21,17</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,17; 14,7</t>
+          <t>6,12; 14,55</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>15,55; 22,28</t>
+          <t>14,81; 21,2</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10,98; 17,69</t>
+          <t>10,52; 17,82</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7,98; 14,42</t>
+          <t>7,65; 13,6</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4,32; 9,18</t>
+          <t>4,31; 9,05</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>10,36; 14,66</t>
+          <t>9,87; 14,26</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,41%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,96; 9,79</t>
+          <t>4,13; 10,28</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8,06; 15,64</t>
+          <t>7,49; 15,15</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,27; 7,08</t>
+          <t>2,34; 7,43</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6,29; 11,43</t>
+          <t>6,25; 11,54</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12,44; 21,97</t>
+          <t>13,11; 22,29</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15,83; 25,34</t>
+          <t>15,86; 25,51</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,36; 17,72</t>
+          <t>9,38; 18,0</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>15,42; 22,24</t>
+          <t>15,15; 21,89</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9,62; 15,04</t>
+          <t>9,47; 14,85</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>13,14; 18,96</t>
+          <t>13,09; 18,87</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6,53; 11,73</t>
+          <t>6,42; 11,47</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>11,52; 15,85</t>
+          <t>11,56; 15,69</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>11,29%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,14; 10,59</t>
+          <t>6,03; 10,6</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,2; 8,32</t>
+          <t>4,28; 8,47</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,45; 5,33</t>
+          <t>2,37; 5,34</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,85; 8,7</t>
+          <t>4,74; 8,3</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>12,11; 17,68</t>
+          <t>11,86; 17,29</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,93; 18,74</t>
+          <t>12,74; 18,29</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,96; 10,41</t>
+          <t>5,93; 10,22</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>14,87; 68,12</t>
+          <t>13,6; 18,4</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>9,78; 13,28</t>
+          <t>9,79; 13,46</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9,32; 12,92</t>
+          <t>9,29; 12,84</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4,61; 7,35</t>
+          <t>4,66; 7,44</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>10,8; 51,36</t>
+          <t>9,78; 12,83</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,73%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>8,58; 12,95</t>
+          <t>8,47; 12,96</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,24; 5,14</t>
+          <t>2,16; 4,95</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,64; 4,31</t>
+          <t>1,56; 4,22</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,95; 3,73</t>
+          <t>2,31; 4,56</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>17,8; 23,48</t>
+          <t>17,81; 23,34</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,18; 11,44</t>
+          <t>7,07; 11,37</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,56; 10,66</t>
+          <t>6,47; 10,83</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>11,12; 15,58</t>
+          <t>10,38; 14,1</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>13,87; 17,64</t>
+          <t>13,94; 17,48</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5,04; 7,6</t>
+          <t>5,08; 7,62</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4,49; 6,98</t>
+          <t>4,44; 6,84</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>4,41; 8,83</t>
+          <t>6,75; 8,92</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>9,94%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6,37; 8,15</t>
+          <t>6,46; 8,17</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4,42; 5,99</t>
+          <t>4,41; 6,04</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,99; 4,3</t>
+          <t>2,96; 4,29</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,95; 5,87</t>
+          <t>4,55; 5,98</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>16,34; 18,97</t>
+          <t>16,39; 19,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,2; 13,51</t>
+          <t>11,3; 13,55</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8,36; 10,45</t>
+          <t>8,41; 10,49</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>13,95; 36,3</t>
+          <t>13,47; 15,23</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>11,68; 13,36</t>
+          <t>11,69; 13,37</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>8,16; 9,57</t>
+          <t>8,2; 9,62</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5,88; 7,16</t>
+          <t>5,94; 7,12</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>9,32; 24,01</t>
+          <t>9,31; 10,46</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9197</t>
+          <t>9238</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>22882</t>
+          <t>24306</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>32079</t>
+          <t>33544</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>9657; 24439</t>
+          <t>9909; 24918</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6634; 21849</t>
+          <t>6713; 22723</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9444; 25147</t>
+          <t>9522; 26447</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4934; 16458</t>
+          <t>4471; 15383</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>24581; 47294</t>
+          <t>24554; 46467</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14025; 34567</t>
+          <t>14571; 34461</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15879; 36527</t>
+          <t>16565; 38078</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>17446; 31214</t>
+          <t>17874; 31345</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>38038; 66156</t>
+          <t>37660; 64879</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>24406; 49091</t>
+          <t>24158; 49724</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>30228; 55907</t>
+          <t>30456; 58017</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>24729; 41326</t>
+          <t>25049; 42210</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>19936</t>
+          <t>20346</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>46549</t>
+          <t>48429</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>66484</t>
+          <t>68775</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14759; 32675</t>
+          <t>15132; 35104</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8024; 26268</t>
+          <t>8207; 25649</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8546; 24009</t>
+          <t>8842; 24769</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12500; 31624</t>
+          <t>12907; 30456</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>76864; 110383</t>
+          <t>74917; 111186</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>37325; 64625</t>
+          <t>37352; 63169</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>37203; 64222</t>
+          <t>36329; 62361</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>37764; 58079</t>
+          <t>38481; 59679</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>94367; 134715</t>
+          <t>97159; 137883</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>50151; 81927</t>
+          <t>48976; 81232</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>49174; 82842</t>
+          <t>49033; 82440</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>53689; 80947</t>
+          <t>54943; 84010</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19492</t>
+          <t>18920</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>55629</t>
+          <t>56605</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>75121</t>
+          <t>75525</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6737; 21333</t>
+          <t>6663; 19378</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>14538; 34082</t>
+          <t>14993; 33268</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7329; 20181</t>
+          <t>6511; 19970</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12967; 28012</t>
+          <t>12991; 27269</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>46988; 75281</t>
+          <t>47881; 76773</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>37286; 64503</t>
+          <t>38371; 65017</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17184; 36571</t>
+          <t>16851; 37240</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>45062; 67872</t>
+          <t>45717; 67098</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>57827; 90433</t>
+          <t>59286; 92922</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>59837; 92301</t>
+          <t>58213; 91146</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>27712; 51853</t>
+          <t>26938; 50687</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>61584; 88470</t>
+          <t>64715; 89480</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>28847</t>
+          <t>31640</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>88008</t>
+          <t>94515</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>116856</t>
+          <t>126156</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>15370; 33784</t>
+          <t>15756; 34931</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9833; 26245</t>
+          <t>9782; 26918</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8904; 24730</t>
+          <t>8898; 25132</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>19850; 40580</t>
+          <t>22595; 43873</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>51069; 80484</t>
+          <t>50744; 77551</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>33167; 58363</t>
+          <t>32733; 58041</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>37711; 66075</t>
+          <t>37423; 66664</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>54087; 113183</t>
+          <t>81158; 110499</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>71954; 107906</t>
+          <t>71284; 106197</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>46868; 77995</t>
+          <t>49828; 78956</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>51043; 82732</t>
+          <t>50330; 82176</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>82133; 138840</t>
+          <t>109191; 144862</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9727</t>
+          <t>10871</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>38627</t>
+          <t>40400</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>48354</t>
+          <t>51270</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>9403; 25650</t>
+          <t>9033; 24608</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5610; 19710</t>
+          <t>5411; 19309</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2485; 13318</t>
+          <t>2705; 13109</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5953; 14835</t>
+          <t>7004; 16717</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>30986; 54938</t>
+          <t>31148; 55619</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>23984; 45830</t>
+          <t>24990; 46485</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13497; 32124</t>
+          <t>13379; 31808</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>32322; 46304</t>
+          <t>33529; 47980</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>45111; 72696</t>
+          <t>43220; 73250</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>34488; 62308</t>
+          <t>33060; 58770</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>18577; 39459</t>
+          <t>18518; 38895</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>40040; 56679</t>
+          <t>42623; 61597</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>23172</t>
+          <t>22761</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>48038</t>
+          <t>48826</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>71210</t>
+          <t>71587</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>10713; 26514</t>
+          <t>11176; 27829</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>22072; 42845</t>
+          <t>20533; 41503</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5968; 18635</t>
+          <t>6166; 19556</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>16947; 30808</t>
+          <t>16927; 31240</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>34603; 61113</t>
+          <t>36457; 61987</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>44011; 70471</t>
+          <t>44111; 70939</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>25554; 48386</t>
+          <t>25607; 49165</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>39526; 57010</t>
+          <t>39871; 57605</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>52834; 82550</t>
+          <t>51988; 81521</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>72562; 104648</t>
+          <t>72252; 104201</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>35030; 62918</t>
+          <t>34409; 61485</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>60573; 83397</t>
+          <t>61703; 83728</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>41072</t>
+          <t>45783</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>304615</t>
+          <t>121326</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>345687</t>
+          <t>167108</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>37788; 65159</t>
+          <t>37068; 65177</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>27846; 55152</t>
+          <t>28339; 56145</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>16076; 35001</t>
+          <t>15593; 35038</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>29988; 53777</t>
+          <t>33840; 59219</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>77295; 112806</t>
+          <t>75719; 110320</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>89704; 130006</t>
+          <t>88381; 126934</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>41198; 71951</t>
+          <t>41008; 70681</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>125775; 576148</t>
+          <t>104346; 141163</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>122582; 166449</t>
+          <t>122691; 168657</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>126389; 175291</t>
+          <t>126005; 174142</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>62077; 99082</t>
+          <t>62812; 100305</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>158146; 751927</t>
+          <t>144834; 189931</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>22121</t>
+          <t>25549</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>92844</t>
+          <t>100360</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>114965</t>
+          <t>125909</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>63811; 96348</t>
+          <t>63025; 96368</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>17423; 40018</t>
+          <t>16832; 38574</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>12783; 33549</t>
+          <t>12121; 32818</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>8856; 34599</t>
+          <t>18421; 36365</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>139463; 183929</t>
+          <t>139530; 182836</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>59061; 94075</t>
+          <t>58171; 93519</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>54203; 88079</t>
+          <t>53418; 89438</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>79584; 111433</t>
+          <t>86231; 117076</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>211806; 269487</t>
+          <t>212843; 266936</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>80683; 121791</t>
+          <t>81292; 122069</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>71990; 112076</t>
+          <t>71320; 109733</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>72426; 145213</t>
+          <t>109873; 145356</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>173564</t>
+          <t>185107</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>697191</t>
+          <t>534768</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>870755</t>
+          <t>719874</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>208868; 267097</t>
+          <t>211644; 267642</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>151392; 205192</t>
+          <t>150975; 206819</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>101492; 146115</t>
+          <t>100603; 145592</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>136351; 202713</t>
+          <t>160410; 210735</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>552263; 640890</t>
+          <t>553969; 642144</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>398302; 480345</t>
+          <t>401719; 481574</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>296250; 370515</t>
+          <t>298270; 371859</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>508592; 1323440</t>
+          <t>500818; 566276</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>777516; 889127</t>
+          <t>778081; 889635</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>569815; 668340</t>
+          <t>572809; 671632</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>408237; 496976</t>
+          <t>412329; 494081</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>661515; 1704021</t>
+          <t>673935; 757593</t>
         </is>
       </c>
     </row>
